--- a/survey_templates/049_management_representation_survey--survey_templates.xlsx
+++ b/survey_templates/049_management_representation_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1114,8 +1114,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Morning'}</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Afternoon'}</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Evening'}</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'1-2'}</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '1-2'}</t>
+          <t>1-2</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'3-5'}</t>
+          <t>3-5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '3-5'}</t>
+          <t>3-5</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'6-10'}</t>
+          <t>6-10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '6-10'}</t>
+          <t>6-10</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Morning'}</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Afternoon'}</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Evening'}</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'less_than_1_hour'}</t>
+          <t>less_than_1_hour</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Less than 1 hour'}</t>
+          <t>Less than 1 hour</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'1-2_hours'}</t>
+          <t>1-2_hours</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '1-2 hours'}</t>
+          <t>1-2 hours</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'3-4_hours'}</t>
+          <t>3-4_hours</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '3-4 hours'}</t>
+          <t>3-4 hours</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1449,12 +1449,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1483,12 +1483,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1517,12 +1517,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1534,12 +1534,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1568,12 +1568,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1636,12 +1636,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1653,12 +1653,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1670,12 +1670,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1687,12 +1687,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1721,12 +1721,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1738,12 +1738,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1772,12 +1772,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1840,12 +1840,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1857,12 +1857,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1891,12 +1891,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
